--- a/SFN/behaviorXpartner.xlsx
+++ b/SFN/behaviorXpartner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324D0CC1-D192-5F40-8338-6D7F72B9C209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0945ECB4-37E0-194C-B6A6-1B3D58594883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{5DFD1542-AFEE-2C42-B457-141A639C727E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>C_def</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>S_rec</t>
-  </si>
-  <si>
-    <t>C_ref</t>
   </si>
   <si>
     <t>average</t>
@@ -437,13 +434,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -461,7 +458,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <f>AVERAGE(Sheet1!B:B)</f>
